--- a/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_indicator_table.xlsx
+++ b/2 Output/Phase1_Baseline_Executive/tables/phase1_baseline_indicator_table.xlsx
@@ -8,13 +8,16 @@
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId2"/>
     <sheet name="indicator_table" sheetId="2" r:id="rId4"/>
+    <sheet name="section10_metrics" sheetId="3" r:id="rId5"/>
+    <sheet name="section10_notes" sheetId="4" r:id="rId6"/>
+    <sheet name="section10_crosswalk" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="163" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1817" uniqueCount="366">
   <si>
     <t>Legatum Phase 1 Final Baseline indicator table</t>
   </si>
@@ -302,13 +305,1190 @@
   </si>
   <si>
     <t>Not measurable</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>idx_respondent_capacity</t>
+  </si>
+  <si>
+    <t>idx_committee_functioning</t>
+  </si>
+  <si>
+    <t>idx_lcc_operational_capacity</t>
+  </si>
+  <si>
+    <t>idx_lcc_case_handling_quality</t>
+  </si>
+  <si>
+    <t>idx_lcc_legitimacy_and_norms</t>
+  </si>
+  <si>
+    <t>idx_p1_base_mentor_ready_proxy</t>
+  </si>
+  <si>
+    <t>high_operational_capacity</t>
+  </si>
+  <si>
+    <t>high_case_handling_quality</t>
+  </si>
+  <si>
+    <t>high_legitimacy_norms</t>
+  </si>
+  <si>
+    <t>high_mentor_readiness_proxy</t>
+  </si>
+  <si>
+    <t>caseload_30d</t>
+  </si>
+  <si>
+    <t>caseload_3m</t>
+  </si>
+  <si>
+    <t>pending_cases</t>
+  </si>
+  <si>
+    <t>directly_brought_cases_3m</t>
+  </si>
+  <si>
+    <t>referred_to_lcc_cases_3m</t>
+  </si>
+  <si>
+    <t>referred_onward_cases_3m</t>
+  </si>
+  <si>
+    <t>pending_share_3m</t>
+  </si>
+  <si>
+    <t>petty_case_share_score</t>
+  </si>
+  <si>
+    <t>prior_formal_coordination</t>
+  </si>
+  <si>
+    <t>referral_frequency_score</t>
+  </si>
+  <si>
+    <t>referral_documentation_score</t>
+  </si>
+  <si>
+    <t>referral_feedback_score</t>
+  </si>
+  <si>
+    <t>police_coordination_score</t>
+  </si>
+  <si>
+    <t>court_coordination_score</t>
+  </si>
+  <si>
+    <t>referral_path_conf_score</t>
+  </si>
+  <si>
+    <t>referral_explain_conf_score</t>
+  </si>
+  <si>
+    <t>verified_referral_record_score</t>
+  </si>
+  <si>
+    <t>verified_ref_dest_score</t>
+  </si>
+  <si>
+    <t>m5_q06_score</t>
+  </si>
+  <si>
+    <t>m5_q07_score</t>
+  </si>
+  <si>
+    <t>m5_q14_score</t>
+  </si>
+  <si>
+    <t>m5_q16_score</t>
+  </si>
+  <si>
+    <t>perceived_lcc_fairness_score</t>
+  </si>
+  <si>
+    <t>perc_willing_use_lcc_score</t>
+  </si>
+  <si>
+    <t>low_bypass_score</t>
+  </si>
+  <si>
+    <t>low_favoritism_influence_score</t>
+  </si>
+  <si>
+    <t>conf_trust_when_referring</t>
+  </si>
+  <si>
+    <t>conf_fair_respect_score</t>
+  </si>
+  <si>
+    <t>reintegration_importance_score</t>
+  </si>
+  <si>
+    <t>reintegration_willingness_score</t>
+  </si>
+  <si>
+    <t>fair_chance_reintegration_score</t>
+  </si>
+  <si>
+    <t>low_exclusion_norm_score</t>
+  </si>
+  <si>
+    <t>low_reoffending_stigma_score</t>
+  </si>
+  <si>
+    <t>connect_support_willing_score</t>
+  </si>
+  <si>
+    <t>reint_comm_justice_role</t>
+  </si>
+  <si>
+    <t>reint_tension_conf_score</t>
+  </si>
+  <si>
+    <t>reint_referral_conf_score</t>
+  </si>
+  <si>
+    <t>recent_reintegration_issue</t>
+  </si>
+  <si>
+    <t>m11_q10_1</t>
+  </si>
+  <si>
+    <t>m11_q10_2</t>
+  </si>
+  <si>
+    <t>m11_q10_3</t>
+  </si>
+  <si>
+    <t>m11_q10_4</t>
+  </si>
+  <si>
+    <t>m11_q10_5</t>
+  </si>
+  <si>
+    <t>m11_q10_6</t>
+  </si>
+  <si>
+    <t>m11_q10_7</t>
+  </si>
+  <si>
+    <t>m11_q10_8</t>
+  </si>
+  <si>
+    <t>m11_q12_1</t>
+  </si>
+  <si>
+    <t>m11_q12_2</t>
+  </si>
+  <si>
+    <t>m11_q12_3</t>
+  </si>
+  <si>
+    <t>m11_q12_4</t>
+  </si>
+  <si>
+    <t>m11_q12_5</t>
+  </si>
+  <si>
+    <t>m11_q12_6</t>
+  </si>
+  <si>
+    <t>m11_q12_7</t>
+  </si>
+  <si>
+    <t>m11_q12_8</t>
+  </si>
+  <si>
+    <t>measure</t>
+  </si>
+  <si>
+    <t>Respondent capacity</t>
+  </si>
+  <si>
+    <t>Legal and classification knowledge</t>
+  </si>
+  <si>
+    <t>Referral practice</t>
+  </si>
+  <si>
+    <t>Record quality</t>
+  </si>
+  <si>
+    <t>Committee functioning</t>
+  </si>
+  <si>
+    <t>Chairperson-perceived legitimacy</t>
+  </si>
+  <si>
+    <t>Safeguards knowledge and perceived special-handling need</t>
+  </si>
+  <si>
+    <t>Chairperson reintegration norms</t>
+  </si>
+  <si>
+    <t>Operational capacity</t>
+  </si>
+  <si>
+    <t>Case-handling quality</t>
+  </si>
+  <si>
+    <t>Legitimacy and reintegration composite</t>
+  </si>
+  <si>
+    <t>Baseline mentor-readiness diagnostic</t>
+  </si>
+  <si>
+    <t>Operational capacity at least 0.75</t>
+  </si>
+  <si>
+    <t>Case-handling quality at least 0.75</t>
+  </si>
+  <si>
+    <t>Legitimacy and norms at least 0.75</t>
+  </si>
+  <si>
+    <t>Baseline mentor proxy at least 0.75</t>
+  </si>
+  <si>
+    <t>Cases received in past 30 days</t>
+  </si>
+  <si>
+    <t>Cases received in past 3 months</t>
+  </si>
+  <si>
+    <t>Cases currently pending or unresolved</t>
+  </si>
+  <si>
+    <t>Reported community-brought cases - respondent scope ambiguous</t>
+  </si>
+  <si>
+    <t>Reported inbound referrals in past 3 months</t>
+  </si>
+  <si>
+    <t>Reported onward referrals in past 3 months</t>
+  </si>
+  <si>
+    <t>Current pending stock divided by recent 3-month inflow</t>
+  </si>
+  <si>
+    <t>Ordinal petty-case composition score</t>
+  </si>
+  <si>
+    <t>Prior formal coordination</t>
+  </si>
+  <si>
+    <t>Reported referral frequency</t>
+  </si>
+  <si>
+    <t>Reported referral documentation</t>
+  </si>
+  <si>
+    <t>Reported receiving-authority feedback</t>
+  </si>
+  <si>
+    <t>Perceived ease of police coordination</t>
+  </si>
+  <si>
+    <t>Perceived ease of court coordination</t>
+  </si>
+  <si>
+    <t>Confidence knowing where to refer</t>
+  </si>
+  <si>
+    <t>Confidence explaining referral</t>
+  </si>
+  <si>
+    <t>Verified referral record score</t>
+  </si>
+  <si>
+    <t>Verified referral destination score</t>
+  </si>
+  <si>
+    <t>Reported agreement documentation</t>
+  </si>
+  <si>
+    <t>Reported follow-up of mediated agreements</t>
+  </si>
+  <si>
+    <t>Reported frequency of agreement compliance</t>
+  </si>
+  <si>
+    <t>Perceived prevention of escalation to police or courts</t>
+  </si>
+  <si>
+    <t>Chairperson-perceived LCC fairness</t>
+  </si>
+  <si>
+    <t>Perceived willingness of community to use LCC</t>
+  </si>
+  <si>
+    <t>Low perceived bypassing</t>
+  </si>
+  <si>
+    <t>Low perceived favoritism</t>
+  </si>
+  <si>
+    <t>Confidence maintaining trust when referring</t>
+  </si>
+  <si>
+    <t>Confidence in fair and respectful handling</t>
+  </si>
+  <si>
+    <t>Importance of reintegration support</t>
+  </si>
+  <si>
+    <t>Willingness to support peaceful return</t>
+  </si>
+  <si>
+    <t>Fair-chance reintegration norm</t>
+  </si>
+  <si>
+    <t>Low exclusion norm</t>
+  </si>
+  <si>
+    <t>Low reoffending stigma</t>
+  </si>
+  <si>
+    <t>Willingness to connect returnees to support</t>
+  </si>
+  <si>
+    <t>Reintegration support viewed as leadership role</t>
+  </si>
+  <si>
+    <t>Confidence reducing reintegration tensions</t>
+  </si>
+  <si>
+    <t>Confidence referring returnees for support</t>
+  </si>
+  <si>
+    <t>Reported reintegration issue in past 6 months</t>
+  </si>
+  <si>
+    <t>Family and community acceptance</t>
+  </si>
+  <si>
+    <t>Livelihood opportunities</t>
+  </si>
+  <si>
+    <t>Psychosocial or emotional support</t>
+  </si>
+  <si>
+    <t>Family or community mediation</t>
+  </si>
+  <si>
+    <t>LC or community leader support</t>
+  </si>
+  <si>
+    <t>Religious or cultural leader support</t>
+  </si>
+  <si>
+    <t>Legal or administrative support</t>
+  </si>
+  <si>
+    <t>Skills training or education</t>
+  </si>
+  <si>
+    <t>Fear of reoffending</t>
+  </si>
+  <si>
+    <t>Fear of violence or conflict</t>
+  </si>
+  <si>
+    <t>Shame or stigma</t>
+  </si>
+  <si>
+    <t>Lack of trust</t>
+  </si>
+  <si>
+    <t>Unresolved victim or family relationships</t>
+  </si>
+  <si>
+    <t>Lack of livelihood</t>
+  </si>
+  <si>
+    <t>Weak support structures</t>
+  </si>
+  <si>
+    <t>Lack of knowledge about reintegration support</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Readiness</t>
+  </si>
+  <si>
+    <t>Caseload</t>
+  </si>
+  <si>
+    <t>Case ratios</t>
+  </si>
+  <si>
+    <t>Referral</t>
+  </si>
+  <si>
+    <t>ADR</t>
+  </si>
+  <si>
+    <t>Legitimacy</t>
+  </si>
+  <si>
+    <t>Reintegration</t>
+  </si>
+  <si>
+    <t>Useful reintegration support</t>
+  </si>
+  <si>
+    <t>Perceived reintegration barriers</t>
+  </si>
+  <si>
+    <t>evidence_type</t>
+  </si>
+  <si>
+    <t>Mixed survey evidence</t>
+  </si>
+  <si>
+    <t>Composite diagnostic</t>
+  </si>
+  <si>
+    <t>Chairperson-reported case counts</t>
+  </si>
+  <si>
+    <t>Self-reported practice</t>
+  </si>
+  <si>
+    <t>Perception / confidence / attitude</t>
+  </si>
+  <si>
+    <t>Verified / enumerator-observed</t>
+  </si>
+  <si>
+    <t>Existing locked index; mean of available components. See Annex B. Not a programme outcome.</t>
+  </si>
+  <si>
+    <t>Existing &gt;=0.75 descriptive threshold; not assessed graduates or final mentor eligibility.</t>
+  </si>
+  <si>
+    <t>Available responses only; no missing-to-zero replacement. Period and case scope differ across measures.</t>
+  </si>
+  <si>
+    <t>Existing ratio/ordinal score; not a verified resolution or diversion rate.</t>
+  </si>
+  <si>
+    <t>Separate cross-sectional items; not a longitudinal referral funnel or administrative case flow.</t>
+  </si>
+  <si>
+    <t>Normalized ordinal response, not objective referral performance.</t>
+  </si>
+  <si>
+    <t>Conditional observed records; cannot generalize verification to all 129 LCs.</t>
+  </si>
+  <si>
+    <t>Ordinal frequency normalized to 0-1; not a verified case-resolution or compliance rate.</t>
+  </si>
+  <si>
+    <t>Assessment normalized to 0-1; not avoided formal-system entries or a causal estimate.</t>
+  </si>
+  <si>
+    <t>LC chairperson perceptions, not direct community respondents.</t>
+  </si>
+  <si>
+    <t>Chairperson norms or assessments; not outcomes experienced by former prisoners.</t>
+  </si>
+  <si>
+    <t>Six-month recall; distinct from the conditional three-month case-type universe.</t>
+  </si>
+  <si>
+    <t>Multiple-response: share of chairpersons selecting option; not share of former prisoners or cases.</t>
+  </si>
+  <si>
+    <t>Score (0-1)</t>
+  </si>
+  <si>
+    <t>Proportion (0-1)</t>
+  </si>
+  <si>
+    <t>Cases</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>median</t>
+  </si>
+  <si>
+    <t>missing_n</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Definition / interpretation</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>129 unique canonical LCs; all selected and consented.</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Sum of observed scores/counts divided by nonmissing N; no imputation.</t>
+  </si>
+  <si>
+    <t>Binary measure</t>
+  </si>
+  <si>
+    <t>Total is the number selecting/meeting the criterion; proportion = total/N.</t>
+  </si>
+  <si>
+    <t>Ordinal score</t>
+  </si>
+  <si>
+    <t>Mean of locked normalized scores, not a percentage of cases or people achieving an outcome.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Sum across observed LC interviews only; missing if N=0. Not population extrapolation.</t>
+  </si>
+  <si>
+    <t>M3_Q09</t>
+  </si>
+  <si>
+    <t>Reported community-brought cases - respondent scope ambiguous. Question excludes disputing parties; hint includes a party. Not formal diversion.</t>
+  </si>
+  <si>
+    <t>Pending ratio</t>
+  </si>
+  <si>
+    <t>Current pending stock/recent inflow; existing valid 0-1 ratios only. Not a closure rate.</t>
+  </si>
+  <si>
+    <t>Petty composition</t>
+  </si>
+  <si>
+    <t>M3_Q06 categories 0-5 divided by 5. Unequal response bands; do not multiply this score by caseload to estimate petty-case totals.</t>
+  </si>
+  <si>
+    <t>Formal indicators</t>
+  </si>
+  <si>
+    <t>Cross-sectional survey benchmarks cannot establish reduction/increase, remand, costs, formal-system flows, graduate performance, or replication.</t>
+  </si>
+  <si>
+    <t>Pending stock exceeds recent inflow: count</t>
+  </si>
+  <si>
+    <t>Pending stock/inflow comparison: N</t>
+  </si>
+  <si>
+    <t>Missing referral counts</t>
+  </si>
+  <si>
+    <t>M3_Q10/M3_Q12 have no observed final values; blank totals are not zero.</t>
+  </si>
+  <si>
+    <t>Existing &gt;=0.75 diagnostic flags only. No assessed graduates, final mentor eligibility or ranking.</t>
+  </si>
+  <si>
+    <t>Reproducibility</t>
+  </si>
+  <si>
+    <t>Data Analysis do-file section 21a; final phase1_baseline_analysis.dta; output sheets section10_metrics and section10_crosswalk.</t>
+  </si>
+  <si>
+    <t>Slide 57 code</t>
+  </si>
+  <si>
+    <t>Revised SOW code</t>
+  </si>
+  <si>
+    <t>Indicator area</t>
+  </si>
+  <si>
+    <t>Survey variable</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>Survey benchmark value</t>
+  </si>
+  <si>
+    <t>Observed N</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Limitation</t>
+  </si>
+  <si>
+    <t>0.0.1</t>
+  </si>
+  <si>
+    <t>Reduction in petty cases entering formal justice</t>
+  </si>
+  <si>
+    <t>Perception benchmark only</t>
+  </si>
+  <si>
+    <t>Perceived prevention of escalation; no formal-system inflow or change observed.</t>
+  </si>
+  <si>
+    <t>0.0.2</t>
+  </si>
+  <si>
+    <t>Reduction of remandees</t>
+  </si>
+  <si>
+    <t>Not measured</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>No prison population or remand-status observations.</t>
+  </si>
+  <si>
+    <t>0.0.3</t>
+  </si>
+  <si>
+    <t>Favourable reintegration conditions</t>
+  </si>
+  <si>
+    <t>Partial proxy</t>
+  </si>
+  <si>
+    <t>Chairperson norms; not observed conditions or reincarceration among former prisoners.</t>
+  </si>
+  <si>
+    <t>0.0.4</t>
+  </si>
+  <si>
+    <t>0.0.4 (cost)</t>
+  </si>
+  <si>
+    <t>Cost per petty case diverted</t>
+  </si>
+  <si>
+    <t>Neither programme costs nor attributable formal entries avoided are observed.</t>
+  </si>
+  <si>
+    <t>0.0.5</t>
+  </si>
+  <si>
+    <t>4.1.2</t>
+  </si>
+  <si>
+    <t>Reduction in case backlog</t>
+  </si>
+  <si>
+    <t>Context benchmark only</t>
+  </si>
+  <si>
+    <t>Current LC pending stock, not formal-court backlog or its reduction.</t>
+  </si>
+  <si>
+    <t>0.0.6</t>
+  </si>
+  <si>
+    <t>0.0.4 (confidence)</t>
+  </si>
+  <si>
+    <t>Increased community confidence</t>
+  </si>
+  <si>
+    <t>Chairperson perceptions, not community respondents or change over time. Duplicate 0.0.4 in Scope of Work remains unresolved.</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>Increase in petty cases resolved through local ADR</t>
+  </si>
+  <si>
+    <t>Cases received of all types, not documented eligible petty-case resolutions.</t>
+  </si>
+  <si>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <t>Increase in cases formally referred to LCC ADR</t>
+  </si>
+  <si>
+    <t>Reported community-brought cases: respondent scope ambiguous. Not formal diversion. Inbound referral counts have N=0.</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Reduction in time on remand</t>
+  </si>
+  <si>
+    <t>No individual remand durations. Scope of Work unit is hours.</t>
+  </si>
+  <si>
+    <t>3.1.4</t>
+  </si>
+  <si>
+    <t>3.1.5</t>
+  </si>
+  <si>
+    <t>Use of prison-acquired skills for income after release</t>
+  </si>
+  <si>
+    <t>Chairpersons are not a sample of trained released prisoners; no income or skills-use outcome.</t>
+  </si>
+  <si>
+    <t>4.1.1</t>
+  </si>
+  <si>
+    <t>JLOS improvements linked to advocacy</t>
+  </si>
+  <si>
+    <t>Mechanism benchmark only</t>
+  </si>
+  <si>
+    <t>Prior LC coordination, not sector reform or an effect of advocacy.</t>
+  </si>
+  <si>
+    <t>4.1.7</t>
+  </si>
+  <si>
+    <t>Not located in revised SOW</t>
+  </si>
+  <si>
+    <t>LC graduates independently executing duties</t>
+  </si>
+  <si>
+    <t>Preparatory diagnostic only</t>
+  </si>
+  <si>
+    <t>Existing baseline &gt;=0.75 proxy; not graduates, assessed competence or final mentor selection.</t>
+  </si>
+  <si>
+    <t>5.1.1</t>
+  </si>
+  <si>
+    <t>Programme models scaled or replicated</t>
+  </si>
+  <si>
+    <t>No survey measure or verified replication inventory. Do not impute zero.</t>
+  </si>
+  <si>
+    <t>Not on Slide 57</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Legal-aid remandees heard within 60 days</t>
+  </si>
+  <si>
+    <t>No linked detention, legal-aid eligibility or first-hearing dates.</t>
+  </si>
+  <si>
+    <t>Self-reported characteristics / literacy</t>
+  </si>
+  <si>
+    <t>Objectively scored knowledge / vignettes</t>
+  </si>
+  <si>
+    <t>Scored knowledge / perceived need</t>
+  </si>
+  <si>
+    <t>Self-reported prior exposure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="83">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -322,7 +1502,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="66">
     <border>
       <left/>
       <right/>
@@ -331,13 +1511,717 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="35" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="41" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="69" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="70" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="71" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="72" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="73" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="74" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="76" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="77" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="78" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="82" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -966,4 +2850,3344 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L73"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K1" t="s">
+        <v>269</v>
+      </c>
+      <c r="L1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G2" s="1">
+        <v>129</v>
+      </c>
+      <c r="H2" s="1">
+        <v>79.716666713356972</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.61795865669268968</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.14834361633210486</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.65238094329833984</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G3" s="1">
+        <v>129</v>
+      </c>
+      <c r="H3" s="1">
+        <v>99.301488518714905</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.76977898076523177</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.15658166235027096</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.8125</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G4" s="1">
+        <v>129</v>
+      </c>
+      <c r="H4" s="1">
+        <v>93.309722423553467</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.72333118157793386</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.13175557959807058</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.74583333730697632</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" t="s">
+        <v>263</v>
+      </c>
+      <c r="G5" s="1">
+        <v>129</v>
+      </c>
+      <c r="H5" s="1">
+        <v>86.707045458257198</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.67214763921129617</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.18975516907361803</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.69090908765792847</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" s="1">
+        <v>129</v>
+      </c>
+      <c r="H6" s="1">
+        <v>81.169047579169273</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.62921742309433548</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.15414998951779244</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.6428571343421936</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" s="1">
+        <v>129</v>
+      </c>
+      <c r="H7" s="1">
+        <v>70.978240486234427</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.55021891849794125</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.2416237734567393</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.61805558204650879</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" t="s">
+        <v>263</v>
+      </c>
+      <c r="G8" s="1">
+        <v>129</v>
+      </c>
+      <c r="H8" s="1">
+        <v>98.387237131595612</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.76269176071004352</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.1283764037768558</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.78666669130325317</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G9" s="1">
+        <v>129</v>
+      </c>
+      <c r="H9" s="1">
+        <v>79.266666680574417</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.61447028434553808</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.14612886355649032</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" t="s">
+        <v>250</v>
+      </c>
+      <c r="F10" t="s">
+        <v>263</v>
+      </c>
+      <c r="G10" s="1">
+        <v>129</v>
+      </c>
+      <c r="H10" s="1">
+        <v>92.506945684552193</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.71710810608179998</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.22415889506941369</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.6736111044883728</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F11" t="s">
+        <v>263</v>
+      </c>
+      <c r="G11" s="1">
+        <v>129</v>
+      </c>
+      <c r="H11" s="1">
+        <v>81.499053031206131</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.63177560489307083</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.11150545593281025</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.64583331346511841</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E12" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" t="s">
+        <v>263</v>
+      </c>
+      <c r="G12" s="1">
+        <v>129</v>
+      </c>
+      <c r="H12" s="1">
+        <v>89.55565556883812</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.69422988813052811</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.13493781087559883</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.73148149251937866</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" t="s">
+        <v>263</v>
+      </c>
+      <c r="G13" s="1">
+        <v>129</v>
+      </c>
+      <c r="H13" s="1">
+        <v>88.423190236091614</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.68545108710148539</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.12346941073279899</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.67168563604354858</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" t="s">
+        <v>244</v>
+      </c>
+      <c r="E14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F14" t="s">
+        <v>263</v>
+      </c>
+      <c r="G14" s="1">
+        <v>129</v>
+      </c>
+      <c r="H14" s="1">
+        <v>80.382859855890274</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.6231229446193044</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.11285709954851184</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0.63541668653488159</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F15" t="s">
+        <v>263</v>
+      </c>
+      <c r="G15" s="1">
+        <v>129</v>
+      </c>
+      <c r="H15" s="1">
+        <v>84.519592851400375</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.65519064225891765</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.092968896421936453</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0.65831387042999268</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F16" t="s">
+        <v>264</v>
+      </c>
+      <c r="G16" s="1">
+        <v>129</v>
+      </c>
+      <c r="H16" s="1">
+        <v>47</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.36434108527131781</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.48312111085310483</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
+        <v>234</v>
+      </c>
+      <c r="D17" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" t="s">
+        <v>264</v>
+      </c>
+      <c r="G17" s="1">
+        <v>129</v>
+      </c>
+      <c r="H17" s="1">
+        <v>42</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.32558139534883723</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.47041854199336447</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" t="s">
+        <v>234</v>
+      </c>
+      <c r="D18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" t="s">
+        <v>251</v>
+      </c>
+      <c r="F18" t="s">
+        <v>264</v>
+      </c>
+      <c r="G18" s="1">
+        <v>129</v>
+      </c>
+      <c r="H18" s="1">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.10077519379844961</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.30220443309098721</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" t="s">
+        <v>251</v>
+      </c>
+      <c r="F19" t="s">
+        <v>264</v>
+      </c>
+      <c r="G19" s="1">
+        <v>129</v>
+      </c>
+      <c r="H19" s="1">
+        <v>18</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.13953488372093023</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.34785472107870574</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F20" t="s">
+        <v>265</v>
+      </c>
+      <c r="G20" s="1">
+        <v>129</v>
+      </c>
+      <c r="H20" s="1">
+        <v>109</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.84496124031007747</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.3604319879356153</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" t="s">
+        <v>246</v>
+      </c>
+      <c r="E21" t="s">
+        <v>252</v>
+      </c>
+      <c r="F21" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" s="1">
+        <v>127</v>
+      </c>
+      <c r="H21" s="1">
+        <v>252</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1.984251968503937</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2.510246468543158</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2</v>
+      </c>
+      <c r="L21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" t="s">
+        <v>235</v>
+      </c>
+      <c r="D22" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F22" t="s">
+        <v>265</v>
+      </c>
+      <c r="G22" s="1">
+        <v>129</v>
+      </c>
+      <c r="H22" s="1">
+        <v>33</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.59000886867595392</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" t="s">
+        <v>235</v>
+      </c>
+      <c r="D23" t="s">
+        <v>246</v>
+      </c>
+      <c r="E23" t="s">
+        <v>252</v>
+      </c>
+      <c r="F23" t="s">
+        <v>265</v>
+      </c>
+      <c r="G23" s="1">
+        <v>89</v>
+      </c>
+      <c r="H23" s="1">
+        <v>18</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0.20224719101123595</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.50406924309921031</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E24" t="s">
+        <v>252</v>
+      </c>
+      <c r="F24" t="s">
+        <v>265</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C25" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" t="s">
+        <v>246</v>
+      </c>
+      <c r="E25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E26" t="s">
+        <v>253</v>
+      </c>
+      <c r="F26" t="s">
+        <v>263</v>
+      </c>
+      <c r="G26" s="1">
+        <v>85</v>
+      </c>
+      <c r="H26" s="1">
+        <v>7.9500000000000002</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0.093529411764705889</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.22218393694479824</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" t="s">
+        <v>236</v>
+      </c>
+      <c r="D27" t="s">
+        <v>247</v>
+      </c>
+      <c r="E27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F27" t="s">
+        <v>263</v>
+      </c>
+      <c r="G27" s="1">
+        <v>89</v>
+      </c>
+      <c r="H27" s="1">
+        <v>47.600000000000001</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0.53483146067415732</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.34611516856108671</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="L27" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" t="s">
+        <v>237</v>
+      </c>
+      <c r="D28" t="s">
+        <v>365</v>
+      </c>
+      <c r="E28" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" t="s">
+        <v>264</v>
+      </c>
+      <c r="G28" s="1">
+        <v>129</v>
+      </c>
+      <c r="H28" s="1">
+        <v>114</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.3218090217996194</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>237</v>
+      </c>
+      <c r="D29" t="s">
+        <v>247</v>
+      </c>
+      <c r="E29" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" t="s">
+        <v>263</v>
+      </c>
+      <c r="G29" s="1">
+        <v>121</v>
+      </c>
+      <c r="H29" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0.76446280991735538</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.27819642465118999</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" t="s">
+        <v>237</v>
+      </c>
+      <c r="D30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E30" t="s">
+        <v>254</v>
+      </c>
+      <c r="F30" t="s">
+        <v>263</v>
+      </c>
+      <c r="G30" s="1">
+        <v>125</v>
+      </c>
+      <c r="H30" s="1">
+        <v>61</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.28014972955143458</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L30" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" t="s">
+        <v>237</v>
+      </c>
+      <c r="D31" t="s">
+        <v>247</v>
+      </c>
+      <c r="E31" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" t="s">
+        <v>263</v>
+      </c>
+      <c r="G31" s="1">
+        <v>122</v>
+      </c>
+      <c r="H31" s="1">
+        <v>55</v>
+      </c>
+      <c r="I31" s="1">
+        <v>0.45081967213114754</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.28320652209167696</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="L31" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" t="s">
+        <v>237</v>
+      </c>
+      <c r="D32" t="s">
+        <v>248</v>
+      </c>
+      <c r="E32" t="s">
+        <v>255</v>
+      </c>
+      <c r="F32" t="s">
+        <v>263</v>
+      </c>
+      <c r="G32" s="1">
+        <v>126</v>
+      </c>
+      <c r="H32" s="1">
+        <v>95.25</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.75595238095238093</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.27832406599912574</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L32" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" t="s">
+        <v>237</v>
+      </c>
+      <c r="D33" t="s">
+        <v>248</v>
+      </c>
+      <c r="E33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" t="s">
+        <v>263</v>
+      </c>
+      <c r="G33" s="1">
+        <v>123</v>
+      </c>
+      <c r="H33" s="1">
+        <v>88.75</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0.72154471544715448</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.30231899481091812</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" t="s">
+        <v>237</v>
+      </c>
+      <c r="D34" t="s">
+        <v>248</v>
+      </c>
+      <c r="E34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F34" t="s">
+        <v>263</v>
+      </c>
+      <c r="G34" s="1">
+        <v>129</v>
+      </c>
+      <c r="H34" s="1">
+        <v>78.5</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0.60852713178294571</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0.20926993922023371</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" t="s">
+        <v>237</v>
+      </c>
+      <c r="D35" t="s">
+        <v>248</v>
+      </c>
+      <c r="E35" t="s">
+        <v>255</v>
+      </c>
+      <c r="F35" t="s">
+        <v>263</v>
+      </c>
+      <c r="G35" s="1">
+        <v>129</v>
+      </c>
+      <c r="H35" s="1">
+        <v>78</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.60465116279069764</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.21807412197328366</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" t="s">
+        <v>237</v>
+      </c>
+      <c r="D36" t="s">
+        <v>249</v>
+      </c>
+      <c r="E36" t="s">
+        <v>256</v>
+      </c>
+      <c r="F36" t="s">
+        <v>263</v>
+      </c>
+      <c r="G36" s="1">
+        <v>74</v>
+      </c>
+      <c r="H36" s="1">
+        <v>51</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0.68918918918918914</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.41133513569123664</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" t="s">
+        <v>237</v>
+      </c>
+      <c r="D37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" t="s">
+        <v>256</v>
+      </c>
+      <c r="F37" t="s">
+        <v>263</v>
+      </c>
+      <c r="G37" s="1">
+        <v>75</v>
+      </c>
+      <c r="H37" s="1">
+        <v>52</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0.69333333333333336</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0.418276170675494</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s">
+        <v>196</v>
+      </c>
+      <c r="C38" t="s">
+        <v>238</v>
+      </c>
+      <c r="D38" t="s">
+        <v>247</v>
+      </c>
+      <c r="E38" t="s">
+        <v>257</v>
+      </c>
+      <c r="F38" t="s">
+        <v>263</v>
+      </c>
+      <c r="G38" s="1">
+        <v>123</v>
+      </c>
+      <c r="H38" s="1">
+        <v>85.25</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0.69308943089430897</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.31495024348456208</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C39" t="s">
+        <v>238</v>
+      </c>
+      <c r="D39" t="s">
+        <v>247</v>
+      </c>
+      <c r="E39" t="s">
+        <v>257</v>
+      </c>
+      <c r="F39" t="s">
+        <v>263</v>
+      </c>
+      <c r="G39" s="1">
+        <v>124</v>
+      </c>
+      <c r="H39" s="1">
+        <v>78.5</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.63306451612903225</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.30315999001132454</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L39" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" t="s">
+        <v>238</v>
+      </c>
+      <c r="D40" t="s">
+        <v>247</v>
+      </c>
+      <c r="E40" t="s">
+        <v>257</v>
+      </c>
+      <c r="F40" t="s">
+        <v>263</v>
+      </c>
+      <c r="G40" s="1">
+        <v>122</v>
+      </c>
+      <c r="H40" s="1">
+        <v>88</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0.72131147540983609</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.29667008924173288</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L40" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" t="s">
+        <v>258</v>
+      </c>
+      <c r="F41" t="s">
+        <v>263</v>
+      </c>
+      <c r="G41" s="1">
+        <v>125</v>
+      </c>
+      <c r="H41" s="1">
+        <v>75.5</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.31779228354991718</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L41" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" t="s">
+        <v>239</v>
+      </c>
+      <c r="D42" t="s">
+        <v>248</v>
+      </c>
+      <c r="E42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" t="s">
+        <v>263</v>
+      </c>
+      <c r="G42" s="1">
+        <v>122</v>
+      </c>
+      <c r="H42" s="1">
+        <v>83.25</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0.68237704918032782</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0.24485804043317513</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L42" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" t="s">
+        <v>248</v>
+      </c>
+      <c r="E43" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" t="s">
+        <v>263</v>
+      </c>
+      <c r="G43" s="1">
+        <v>122</v>
+      </c>
+      <c r="H43" s="1">
+        <v>83.5</v>
+      </c>
+      <c r="I43" s="1">
+        <v>0.68442622950819676</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0.23133478720057857</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L43" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" t="s">
+        <v>239</v>
+      </c>
+      <c r="D44" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" t="s">
+        <v>259</v>
+      </c>
+      <c r="F44" t="s">
+        <v>263</v>
+      </c>
+      <c r="G44" s="1">
+        <v>122</v>
+      </c>
+      <c r="H44" s="1">
+        <v>61.25</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0.50204918032786883</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.29719053221349284</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L44" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C45" t="s">
+        <v>239</v>
+      </c>
+      <c r="D45" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" t="s">
+        <v>263</v>
+      </c>
+      <c r="G45" s="1">
+        <v>121</v>
+      </c>
+      <c r="H45" s="1">
+        <v>72.25</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0.59710743801652888</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0.30511592883287525</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L45" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" t="s">
+        <v>239</v>
+      </c>
+      <c r="D46" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" t="s">
+        <v>259</v>
+      </c>
+      <c r="F46" t="s">
+        <v>263</v>
+      </c>
+      <c r="G46" s="1">
+        <v>129</v>
+      </c>
+      <c r="H46" s="1">
+        <v>80.5</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0.62403100775193798</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0.19546626699000458</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" t="s">
+        <v>248</v>
+      </c>
+      <c r="E47" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" t="s">
+        <v>263</v>
+      </c>
+      <c r="G47" s="1">
+        <v>129</v>
+      </c>
+      <c r="H47" s="1">
+        <v>81.25</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0.62984496124031009</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0.21217984889049618</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" t="s">
+        <v>206</v>
+      </c>
+      <c r="C48" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" t="s">
+        <v>248</v>
+      </c>
+      <c r="E48" t="s">
+        <v>260</v>
+      </c>
+      <c r="F48" t="s">
+        <v>263</v>
+      </c>
+      <c r="G48" s="1">
+        <v>129</v>
+      </c>
+      <c r="H48" s="1">
+        <v>83.25</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0.64534883720930236</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0.21807412197328366</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" t="s">
+        <v>207</v>
+      </c>
+      <c r="C49" t="s">
+        <v>240</v>
+      </c>
+      <c r="D49" t="s">
+        <v>248</v>
+      </c>
+      <c r="E49" t="s">
+        <v>260</v>
+      </c>
+      <c r="F49" t="s">
+        <v>263</v>
+      </c>
+      <c r="G49" s="1">
+        <v>129</v>
+      </c>
+      <c r="H49" s="1">
+        <v>86</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0.19846415503393386</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>137</v>
+      </c>
+      <c r="B50" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" t="s">
+        <v>240</v>
+      </c>
+      <c r="D50" t="s">
+        <v>248</v>
+      </c>
+      <c r="E50" t="s">
+        <v>260</v>
+      </c>
+      <c r="F50" t="s">
+        <v>263</v>
+      </c>
+      <c r="G50" s="1">
+        <v>129</v>
+      </c>
+      <c r="H50" s="1">
+        <v>99.25</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0.76937984496124034</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.15503402821026349</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D51" t="s">
+        <v>248</v>
+      </c>
+      <c r="E51" t="s">
+        <v>260</v>
+      </c>
+      <c r="F51" t="s">
+        <v>263</v>
+      </c>
+      <c r="G51" s="1">
+        <v>129</v>
+      </c>
+      <c r="H51" s="1">
+        <v>68.5</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0.53100775193798455</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.31407066522032584</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" t="s">
+        <v>210</v>
+      </c>
+      <c r="C52" t="s">
+        <v>240</v>
+      </c>
+      <c r="D52" t="s">
+        <v>248</v>
+      </c>
+      <c r="E52" t="s">
+        <v>260</v>
+      </c>
+      <c r="F52" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52" s="1">
+        <v>128</v>
+      </c>
+      <c r="H52" s="1">
+        <v>55</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0.4296875</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.24288598634380848</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" t="s">
+        <v>211</v>
+      </c>
+      <c r="C53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D53" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" t="s">
+        <v>260</v>
+      </c>
+      <c r="F53" t="s">
+        <v>263</v>
+      </c>
+      <c r="G53" s="1">
+        <v>128</v>
+      </c>
+      <c r="H53" s="1">
+        <v>93.75</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0.732421875</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0.18072359411674072</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" t="s">
+        <v>248</v>
+      </c>
+      <c r="E54" t="s">
+        <v>260</v>
+      </c>
+      <c r="F54" t="s">
+        <v>264</v>
+      </c>
+      <c r="G54" s="1">
+        <v>129</v>
+      </c>
+      <c r="H54" s="1">
+        <v>117</v>
+      </c>
+      <c r="I54" s="1">
+        <v>0.90697674418604646</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0.29159744472035737</v>
+      </c>
+      <c r="K54" s="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>142</v>
+      </c>
+      <c r="B55" t="s">
+        <v>213</v>
+      </c>
+      <c r="C55" t="s">
+        <v>240</v>
+      </c>
+      <c r="D55" t="s">
+        <v>248</v>
+      </c>
+      <c r="E55" t="s">
+        <v>260</v>
+      </c>
+      <c r="F55" t="s">
+        <v>263</v>
+      </c>
+      <c r="G55" s="1">
+        <v>129</v>
+      </c>
+      <c r="H55" s="1">
+        <v>80.25</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0.62209302325581395</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0.2212276627799285</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" t="s">
+        <v>248</v>
+      </c>
+      <c r="E56" t="s">
+        <v>260</v>
+      </c>
+      <c r="F56" t="s">
+        <v>263</v>
+      </c>
+      <c r="G56" s="1">
+        <v>129</v>
+      </c>
+      <c r="H56" s="1">
+        <v>78.25</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0.60658914728682167</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0.21824762356964728</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" t="s">
+        <v>215</v>
+      </c>
+      <c r="C57" t="s">
+        <v>240</v>
+      </c>
+      <c r="D57" t="s">
+        <v>247</v>
+      </c>
+      <c r="E57" t="s">
+        <v>261</v>
+      </c>
+      <c r="F57" t="s">
+        <v>264</v>
+      </c>
+      <c r="G57" s="1">
+        <v>129</v>
+      </c>
+      <c r="H57" s="1">
+        <v>55</v>
+      </c>
+      <c r="I57" s="1">
+        <v>0.4263565891472868</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0.49647497731585144</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" t="s">
+        <v>216</v>
+      </c>
+      <c r="C58" t="s">
+        <v>241</v>
+      </c>
+      <c r="D58" t="s">
+        <v>248</v>
+      </c>
+      <c r="E58" t="s">
+        <v>262</v>
+      </c>
+      <c r="F58" t="s">
+        <v>264</v>
+      </c>
+      <c r="G58" s="1">
+        <v>129</v>
+      </c>
+      <c r="H58" s="1">
+        <v>110</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0.8527131782945736</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0.35577325982021296</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>217</v>
+      </c>
+      <c r="C59" t="s">
+        <v>241</v>
+      </c>
+      <c r="D59" t="s">
+        <v>248</v>
+      </c>
+      <c r="E59" t="s">
+        <v>262</v>
+      </c>
+      <c r="F59" t="s">
+        <v>264</v>
+      </c>
+      <c r="G59" s="1">
+        <v>129</v>
+      </c>
+      <c r="H59" s="1">
+        <v>38</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0.29457364341085274</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0.45762806908274661</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>218</v>
+      </c>
+      <c r="C60" t="s">
+        <v>241</v>
+      </c>
+      <c r="D60" t="s">
+        <v>248</v>
+      </c>
+      <c r="E60" t="s">
+        <v>262</v>
+      </c>
+      <c r="F60" t="s">
+        <v>264</v>
+      </c>
+      <c r="G60" s="1">
+        <v>129</v>
+      </c>
+      <c r="H60" s="1">
+        <v>73</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0.56589147286821706</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.49757162236189167</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>148</v>
+      </c>
+      <c r="B61" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" t="s">
+        <v>241</v>
+      </c>
+      <c r="D61" t="s">
+        <v>248</v>
+      </c>
+      <c r="E61" t="s">
+        <v>262</v>
+      </c>
+      <c r="F61" t="s">
+        <v>264</v>
+      </c>
+      <c r="G61" s="1">
+        <v>129</v>
+      </c>
+      <c r="H61" s="1">
+        <v>14</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0.10852713178294574</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0.31225765797052973</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>149</v>
+      </c>
+      <c r="B62" t="s">
+        <v>220</v>
+      </c>
+      <c r="C62" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" t="s">
+        <v>248</v>
+      </c>
+      <c r="E62" t="s">
+        <v>262</v>
+      </c>
+      <c r="F62" t="s">
+        <v>264</v>
+      </c>
+      <c r="G62" s="1">
+        <v>129</v>
+      </c>
+      <c r="H62" s="1">
+        <v>30</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0.42410987496934283</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" t="s">
+        <v>241</v>
+      </c>
+      <c r="D63" t="s">
+        <v>248</v>
+      </c>
+      <c r="E63" t="s">
+        <v>262</v>
+      </c>
+      <c r="F63" t="s">
+        <v>264</v>
+      </c>
+      <c r="G63" s="1">
+        <v>129</v>
+      </c>
+      <c r="H63" s="1">
+        <v>11</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0.085271317829457363</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0.28037385064237175</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" t="s">
+        <v>222</v>
+      </c>
+      <c r="C64" t="s">
+        <v>241</v>
+      </c>
+      <c r="D64" t="s">
+        <v>248</v>
+      </c>
+      <c r="E64" t="s">
+        <v>262</v>
+      </c>
+      <c r="F64" t="s">
+        <v>264</v>
+      </c>
+      <c r="G64" s="1">
+        <v>129</v>
+      </c>
+      <c r="H64" s="1">
+        <v>3</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0.15130248464736168</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>152</v>
+      </c>
+      <c r="B65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" t="s">
+        <v>241</v>
+      </c>
+      <c r="D65" t="s">
+        <v>248</v>
+      </c>
+      <c r="E65" t="s">
+        <v>262</v>
+      </c>
+      <c r="F65" t="s">
+        <v>264</v>
+      </c>
+      <c r="G65" s="1">
+        <v>129</v>
+      </c>
+      <c r="H65" s="1">
+        <v>7</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0.054263565891472868</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0.22742023049920179</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" t="s">
+        <v>242</v>
+      </c>
+      <c r="D66" t="s">
+        <v>248</v>
+      </c>
+      <c r="E66" t="s">
+        <v>262</v>
+      </c>
+      <c r="F66" t="s">
+        <v>264</v>
+      </c>
+      <c r="G66" s="1">
+        <v>129</v>
+      </c>
+      <c r="H66" s="1">
+        <v>70</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0.54263565891472865</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0.50012110936352983</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" t="s">
+        <v>225</v>
+      </c>
+      <c r="C67" t="s">
+        <v>242</v>
+      </c>
+      <c r="D67" t="s">
+        <v>248</v>
+      </c>
+      <c r="E67" t="s">
+        <v>262</v>
+      </c>
+      <c r="F67" t="s">
+        <v>264</v>
+      </c>
+      <c r="G67" s="1">
+        <v>129</v>
+      </c>
+      <c r="H67" s="1">
+        <v>43</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0.47324236215002285</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" t="s">
+        <v>226</v>
+      </c>
+      <c r="C68" t="s">
+        <v>242</v>
+      </c>
+      <c r="D68" t="s">
+        <v>248</v>
+      </c>
+      <c r="E68" t="s">
+        <v>262</v>
+      </c>
+      <c r="F68" t="s">
+        <v>264</v>
+      </c>
+      <c r="G68" s="1">
+        <v>129</v>
+      </c>
+      <c r="H68" s="1">
+        <v>17</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0.13178294573643412</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0.33957337575166263</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" t="s">
+        <v>242</v>
+      </c>
+      <c r="D69" t="s">
+        <v>248</v>
+      </c>
+      <c r="E69" t="s">
+        <v>262</v>
+      </c>
+      <c r="F69" t="s">
+        <v>264</v>
+      </c>
+      <c r="G69" s="1">
+        <v>129</v>
+      </c>
+      <c r="H69" s="1">
+        <v>25</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0.19379844961240311</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0.3968138610357223</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" t="s">
+        <v>228</v>
+      </c>
+      <c r="C70" t="s">
+        <v>242</v>
+      </c>
+      <c r="D70" t="s">
+        <v>248</v>
+      </c>
+      <c r="E70" t="s">
+        <v>262</v>
+      </c>
+      <c r="F70" t="s">
+        <v>264</v>
+      </c>
+      <c r="G70" s="1">
+        <v>129</v>
+      </c>
+      <c r="H70" s="1">
+        <v>5</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0.03875968992248062</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0.19377422329196189</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" t="s">
+        <v>229</v>
+      </c>
+      <c r="C71" t="s">
+        <v>242</v>
+      </c>
+      <c r="D71" t="s">
+        <v>248</v>
+      </c>
+      <c r="E71" t="s">
+        <v>262</v>
+      </c>
+      <c r="F71" t="s">
+        <v>264</v>
+      </c>
+      <c r="G71" s="1">
+        <v>129</v>
+      </c>
+      <c r="H71" s="1">
+        <v>5</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0.03875968992248062</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0.19377422329196189</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" t="s">
+        <v>230</v>
+      </c>
+      <c r="C72" t="s">
+        <v>242</v>
+      </c>
+      <c r="D72" t="s">
+        <v>248</v>
+      </c>
+      <c r="E72" t="s">
+        <v>262</v>
+      </c>
+      <c r="F72" t="s">
+        <v>264</v>
+      </c>
+      <c r="G72" s="1">
+        <v>129</v>
+      </c>
+      <c r="H72" s="1">
+        <v>5</v>
+      </c>
+      <c r="I72" s="1">
+        <v>0.03875968992248062</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0.19377422329196189</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>160</v>
+      </c>
+      <c r="B73" t="s">
+        <v>231</v>
+      </c>
+      <c r="C73" t="s">
+        <v>242</v>
+      </c>
+      <c r="D73" t="s">
+        <v>248</v>
+      </c>
+      <c r="E73" t="s">
+        <v>262</v>
+      </c>
+      <c r="F73" t="s">
+        <v>264</v>
+      </c>
+      <c r="G73" s="1">
+        <v>129</v>
+      </c>
+      <c r="H73" s="1">
+        <v>3</v>
+      </c>
+      <c r="I73" s="1">
+        <v>0.023255813953488372</v>
+      </c>
+      <c r="J73" s="1">
+        <v>0.15130248464736168</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B13" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B15" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>302</v>
+      </c>
+      <c r="F1" s="48" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1" s="49" t="s">
+        <v>304</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" s="52">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="G2">
+        <v>125</v>
+      </c>
+      <c r="H2" t="s">
+        <v>309</v>
+      </c>
+      <c r="I2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>313</v>
+      </c>
+      <c r="G3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F4" s="54">
+        <v>0.63177560489307083</v>
+      </c>
+      <c r="G4">
+        <v>129</v>
+      </c>
+      <c r="H4" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>313</v>
+      </c>
+      <c r="G5" t="s">
+        <v>314</v>
+      </c>
+      <c r="H5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="56">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>129</v>
+      </c>
+      <c r="H6" t="s">
+        <v>327</v>
+      </c>
+      <c r="I6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F7" s="57">
+        <v>0.61447028434553808</v>
+      </c>
+      <c r="G7">
+        <v>129</v>
+      </c>
+      <c r="H7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="58">
+        <v>252</v>
+      </c>
+      <c r="G8">
+        <v>127</v>
+      </c>
+      <c r="H8" t="s">
+        <v>327</v>
+      </c>
+      <c r="I8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="59">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>89</v>
+      </c>
+      <c r="H9" t="s">
+        <v>327</v>
+      </c>
+      <c r="I9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="G10" t="s">
+        <v>314</v>
+      </c>
+      <c r="H10" t="s">
+        <v>313</v>
+      </c>
+      <c r="I10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" t="s">
+        <v>314</v>
+      </c>
+      <c r="H11" t="s">
+        <v>313</v>
+      </c>
+      <c r="I11" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F12" s="62">
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="G12">
+        <v>129</v>
+      </c>
+      <c r="H12" t="s">
+        <v>348</v>
+      </c>
+      <c r="I12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>350</v>
+      </c>
+      <c r="B13" t="s">
+        <v>351</v>
+      </c>
+      <c r="C13" t="s">
+        <v>352</v>
+      </c>
+      <c r="D13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" t="s">
+        <v>267</v>
+      </c>
+      <c r="F13" s="63">
+        <v>0.13953488372093023</v>
+      </c>
+      <c r="G13">
+        <v>129</v>
+      </c>
+      <c r="H13" t="s">
+        <v>353</v>
+      </c>
+      <c r="I13" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="G14" t="s">
+        <v>314</v>
+      </c>
+      <c r="H14" t="s">
+        <v>313</v>
+      </c>
+      <c r="I14" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" t="s">
+        <v>360</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>313</v>
+      </c>
+      <c r="G15" t="s">
+        <v>314</v>
+      </c>
+      <c r="H15" t="s">
+        <v>313</v>
+      </c>
+      <c r="I15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>